--- a/MASTER_AGGREGATED.xlsx
+++ b/MASTER_AGGREGATED.xlsx
@@ -736,52 +736,52 @@
         <v>1361585515.3</v>
       </c>
       <c r="AF2" s="4" t="n">
-        <v>1259047929.14</v>
+        <v>1259901519.05</v>
       </c>
       <c r="AG2" s="4" t="n">
-        <v>1437526274.01</v>
+        <v>1438908996.41</v>
       </c>
       <c r="AH2" s="4" t="n">
-        <v>2331674099.57</v>
+        <v>2334849870.42</v>
       </c>
       <c r="AI2" s="4" t="n">
-        <v>2377889251.36</v>
+        <v>2380393177.51</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>2422674718.59</v>
+        <v>2426525155.43</v>
       </c>
       <c r="AK2" s="4" t="n">
-        <v>2287207473.73</v>
+        <v>2292325032.04</v>
       </c>
       <c r="AL2" s="4" t="n">
-        <v>2398298254.48</v>
+        <v>2400533593.04</v>
       </c>
       <c r="AM2" s="4" t="n">
-        <v>1953526412</v>
+        <v>1955305208.25</v>
       </c>
       <c r="AN2" s="4" t="n">
-        <v>2418890883.46</v>
+        <v>2421081501.13</v>
       </c>
       <c r="AO2" s="4" t="n">
-        <v>1934555840.88</v>
+        <v>1936121568.75</v>
       </c>
       <c r="AP2" s="4" t="n">
-        <v>1947812598.49</v>
+        <v>1949416599.84</v>
       </c>
       <c r="AQ2" s="4" t="n">
-        <v>1556767482.69</v>
+        <v>1558213900.48</v>
       </c>
       <c r="AR2" s="4" t="n">
-        <v>1442526102.65</v>
+        <v>1443657647.79</v>
       </c>
       <c r="AS2" s="4" t="n">
-        <v>1738593393.81</v>
+        <v>1740065252.36</v>
       </c>
       <c r="AT2" s="4" t="n">
-        <v>2664445305.44</v>
+        <v>2666796239.55</v>
       </c>
       <c r="AU2" s="4" t="n">
-        <v>2549693184.95</v>
+        <v>2552104268.57</v>
       </c>
     </row>
     <row r="3">
@@ -845,19 +845,19 @@
         <v>734932577.88</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>689054338.3200001</v>
+        <v>726470595.7700001</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>727152726.77</v>
+        <v>779409847.3200001</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>1122040697.46</v>
+        <v>1214822790.21</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>1577406993.44</v>
+        <v>1671385631.27</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>1727745710.22</v>
+        <v>1827869113.76</v>
       </c>
       <c r="Y3" s="4" t="n">
         <v>1645683725.53</v>
@@ -881,52 +881,52 @@
         <v>1270612383.5</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>1276995357.78</v>
+        <v>1284093028.26</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>1386272461.17</v>
+        <v>1391964179.17</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>2215879753.2</v>
+        <v>2228358775.2</v>
       </c>
       <c r="AI3" s="4" t="n">
-        <v>2548311055.56</v>
+        <v>2560399823.06</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>2729563162.94</v>
+        <v>2741322289.44</v>
       </c>
       <c r="AK3" s="4" t="n">
-        <v>2681743231.8</v>
+        <v>2692451170.3</v>
       </c>
       <c r="AL3" s="4" t="n">
-        <v>2683235599.37</v>
+        <v>2694013928.87</v>
       </c>
       <c r="AM3" s="4" t="n">
-        <v>2002685472.3</v>
+        <v>2010838699.3</v>
       </c>
       <c r="AN3" s="4" t="n">
-        <v>2433614302.01</v>
+        <v>2443838816.76</v>
       </c>
       <c r="AO3" s="4" t="n">
-        <v>2079127221.33</v>
+        <v>2087710247.83</v>
       </c>
       <c r="AP3" s="4" t="n">
-        <v>1980034005.54</v>
+        <v>1988760877.04</v>
       </c>
       <c r="AQ3" s="4" t="n">
-        <v>1443153627.78</v>
+        <v>1450024884.78</v>
       </c>
       <c r="AR3" s="4" t="n">
-        <v>1305123965.06</v>
+        <v>1312067948.06</v>
       </c>
       <c r="AS3" s="4" t="n">
-        <v>1554810320.67</v>
+        <v>1562832179.42</v>
       </c>
       <c r="AT3" s="4" t="n">
-        <v>2342360532.76</v>
+        <v>2355115109.01</v>
       </c>
       <c r="AU3" s="4" t="n">
-        <v>2535725827.11</v>
+        <v>2546835034.61</v>
       </c>
     </row>
     <row r="4">
@@ -972,106 +972,106 @@
         <v>141473951.74</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>340974926.89</v>
+        <v>343291034.8</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>235672873.7</v>
+        <v>237002488.78</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>321044290.56</v>
+        <v>322387307.81</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>276844185.24</v>
+        <v>277924954.85</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>217936027.33</v>
+        <v>218848098.32</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>179231142.44</v>
+        <v>179789357.3</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>176058228.61</v>
+        <v>176471395.93</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>189486341.84</v>
+        <v>190054935.19</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>297840974.23</v>
+        <v>299112050.62</v>
       </c>
       <c r="W4" s="4" t="n">
-        <v>350032023.2</v>
+        <v>351396927.16</v>
       </c>
       <c r="X4" s="4" t="n">
-        <v>383115513.58</v>
+        <v>385120802.33</v>
       </c>
       <c r="Y4" s="4" t="n">
-        <v>311577060.67</v>
+        <v>313440854.45</v>
       </c>
       <c r="Z4" s="4" t="n">
-        <v>336579132.79</v>
+        <v>338306855.77</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>317464059.89</v>
+        <v>318955866.43</v>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>429559702.29</v>
+        <v>431224955.32</v>
       </c>
       <c r="AC4" s="4" t="n">
-        <v>353995822.04</v>
+        <v>355394821.52</v>
       </c>
       <c r="AD4" s="4" t="n">
-        <v>321271749.59</v>
+        <v>322426342.35</v>
       </c>
       <c r="AE4" s="4" t="n">
-        <v>278340836</v>
+        <v>279067802.42</v>
       </c>
       <c r="AF4" s="4" t="n">
-        <v>239549818.87</v>
+        <v>240159468.47</v>
       </c>
       <c r="AG4" s="4" t="n">
-        <v>312285144.04</v>
+        <v>313164040.38</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>413068002.31</v>
+        <v>414744913.46</v>
       </c>
       <c r="AI4" s="4" t="n">
-        <v>464451280.52</v>
+        <v>466111182.29</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>519582776.51</v>
+        <v>522012437.14</v>
       </c>
       <c r="AK4" s="4" t="n">
-        <v>519557536.77</v>
+        <v>521370305.72</v>
       </c>
       <c r="AL4" s="4" t="n">
-        <v>520076289.1499999</v>
+        <v>521912940.5899999</v>
       </c>
       <c r="AM4" s="4" t="n">
-        <v>388296560.05</v>
+        <v>390075456.27</v>
       </c>
       <c r="AN4" s="4" t="n">
-        <v>493038450.87</v>
+        <v>494755727.88</v>
       </c>
       <c r="AO4" s="4" t="n">
-        <v>388342559.54</v>
+        <v>389807062.16</v>
       </c>
       <c r="AP4" s="4" t="n">
-        <v>390260161.87</v>
+        <v>391342467.4</v>
       </c>
       <c r="AQ4" s="4" t="n">
-        <v>309919803.69</v>
+        <v>310549188.97</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>327821064.13</v>
+        <v>328358759.92</v>
       </c>
       <c r="AS4" s="4" t="n">
-        <v>360609979.41</v>
+        <v>361812431.08</v>
       </c>
       <c r="AT4" s="4" t="n">
-        <v>451264320.87</v>
+        <v>454639967.72</v>
       </c>
       <c r="AU4" s="4" t="n">
-        <v>440275350.09</v>
+        <v>443534420.9</v>
       </c>
     </row>
     <row r="5">
@@ -1171,52 +1171,52 @@
         <v>235105798.99</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>216917669.59</v>
+        <v>218649801.14</v>
       </c>
       <c r="AG5" s="4" t="n">
-        <v>237025568.24</v>
+        <v>238595760.76</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>303035601.0699999</v>
+        <v>304773278.8099999</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>321627008.92</v>
+        <v>323475509.73</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>357480663.12</v>
+        <v>359242397.67</v>
       </c>
       <c r="AK5" s="4" t="n">
-        <v>342078885</v>
+        <v>344000366.37</v>
       </c>
       <c r="AL5" s="4" t="n">
-        <v>351036304.98</v>
+        <v>353129377.59</v>
       </c>
       <c r="AM5" s="4" t="n">
-        <v>280702967.19</v>
+        <v>282185271.53</v>
       </c>
       <c r="AN5" s="4" t="n">
-        <v>347116565.28</v>
+        <v>348799618.73</v>
       </c>
       <c r="AO5" s="4" t="n">
-        <v>303105496.74</v>
+        <v>304508384.27</v>
       </c>
       <c r="AP5" s="4" t="n">
-        <v>286611151.8019994</v>
+        <v>288154312.8819994</v>
       </c>
       <c r="AQ5" s="4" t="n">
-        <v>209465376.1169999</v>
+        <v>210403202.9269999</v>
       </c>
       <c r="AR5" s="4" t="n">
-        <v>216713285.5545</v>
+        <v>217525045.5845</v>
       </c>
       <c r="AS5" s="4" t="n">
-        <v>259830054.4939996</v>
+        <v>260781658.6639996</v>
       </c>
       <c r="AT5" s="4" t="n">
-        <v>350908341.7</v>
+        <v>352878028.78</v>
       </c>
       <c r="AU5" s="4" t="n">
-        <v>351423108.76</v>
+        <v>353438969.54</v>
       </c>
     </row>
     <row r="6">
@@ -1422,7 +1422,7 @@
         <v>53121692.25</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>40389178.61</v>
+        <v>40442392.7</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>53799311.78</v>
@@ -1437,73 +1437,73 @@
         <v>193001274.89</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>210049998.47</v>
+        <v>210315989.74</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>226500752.38</v>
+        <v>226731124.69</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>152890923.63</v>
+        <v>152938709</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>198201376.03</v>
+        <v>198295884.23</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>165760880.86</v>
+        <v>165837809.91</v>
       </c>
       <c r="AD7" s="4" t="n">
-        <v>128226994.08</v>
+        <v>128307218.82</v>
       </c>
       <c r="AE7" s="4" t="n">
-        <v>98992005.36</v>
+        <v>99066512.93000001</v>
       </c>
       <c r="AF7" s="4" t="n">
-        <v>101955607.02</v>
+        <v>151103836.64</v>
       </c>
       <c r="AG7" s="4" t="n">
-        <v>113560288.59</v>
+        <v>171025339.93</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>173242528.25</v>
+        <v>261166547.25</v>
       </c>
       <c r="AI7" s="4" t="n">
-        <v>235481412.72</v>
+        <v>339955711.77</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>253263016.47</v>
+        <v>364236415.61</v>
       </c>
       <c r="AK7" s="4" t="n">
-        <v>263431387.34</v>
+        <v>374250306.87</v>
       </c>
       <c r="AL7" s="4" t="n">
-        <v>279267232.02</v>
+        <v>390752618.53</v>
       </c>
       <c r="AM7" s="4" t="n">
-        <v>270013849.21</v>
+        <v>357891242.89</v>
       </c>
       <c r="AN7" s="4" t="n">
-        <v>283403881.57</v>
+        <v>398274230.97</v>
       </c>
       <c r="AO7" s="4" t="n">
-        <v>218096504.93</v>
+        <v>311392611.02</v>
       </c>
       <c r="AP7" s="4" t="n">
-        <v>211524972.42</v>
+        <v>292390662.21</v>
       </c>
       <c r="AQ7" s="4" t="n">
-        <v>174791847.27</v>
+        <v>246330543.87</v>
       </c>
       <c r="AR7" s="4" t="n">
-        <v>151652012.67</v>
+        <v>204342270.99</v>
       </c>
       <c r="AS7" s="4" t="n">
-        <v>192967815.34</v>
+        <v>253285446.28</v>
       </c>
       <c r="AT7" s="4" t="n">
-        <v>264117764.97</v>
+        <v>358154820.88</v>
       </c>
       <c r="AU7" s="4" t="n">
-        <v>275615212.69</v>
+        <v>374786694.55</v>
       </c>
     </row>
     <row r="8">
@@ -1585,70 +1585,70 @@
         <v>432364443.1</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>448424827.92</v>
+        <v>453774528.11</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>409732296.05</v>
+        <v>412385228.14</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>511840232.27</v>
+        <v>515504722.99</v>
       </c>
       <c r="AC8" s="4" t="n">
-        <v>423056603.17</v>
+        <v>426059938.36</v>
       </c>
       <c r="AD8" s="4" t="n">
-        <v>364534319.5</v>
+        <v>367467035.03</v>
       </c>
       <c r="AE8" s="4" t="n">
-        <v>349460865.32</v>
+        <v>351611338.38</v>
       </c>
       <c r="AF8" s="4" t="n">
-        <v>316505714.86</v>
+        <v>344061853.57</v>
       </c>
       <c r="AG8" s="4" t="n">
-        <v>374262217.03</v>
+        <v>408884554.54</v>
       </c>
       <c r="AH8" s="4" t="n">
-        <v>526752354.67</v>
+        <v>572190476.95</v>
       </c>
       <c r="AI8" s="4" t="n">
-        <v>578452360.14</v>
+        <v>624200970.6</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>629136318.6799999</v>
+        <v>680472177.97</v>
       </c>
       <c r="AK8" s="4" t="n">
-        <v>594147880.95</v>
+        <v>639035314.96</v>
       </c>
       <c r="AL8" s="4" t="n">
-        <v>606190675.77</v>
+        <v>652957149.23</v>
       </c>
       <c r="AM8" s="4" t="n">
-        <v>465037882.26</v>
+        <v>498272353.42</v>
       </c>
       <c r="AN8" s="4" t="n">
-        <v>597445064.2</v>
+        <v>637537844.51</v>
       </c>
       <c r="AO8" s="4" t="n">
-        <v>505635024.63</v>
+        <v>539906484.26</v>
       </c>
       <c r="AP8" s="4" t="n">
-        <v>399013513.89</v>
+        <v>502405863.33</v>
       </c>
       <c r="AQ8" s="4" t="n">
-        <v>314117132.22</v>
+        <v>399326397.09</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>253968249.37</v>
+        <v>276413508.98</v>
       </c>
       <c r="AS8" s="4" t="n">
-        <v>302540745.47</v>
+        <v>330496987.18</v>
       </c>
       <c r="AT8" s="4" t="n">
-        <v>449173973.64</v>
+        <v>489471772.08</v>
       </c>
       <c r="AU8" s="4" t="n">
-        <v>337487078.62</v>
+        <v>381244863.91</v>
       </c>
     </row>
   </sheetData>
@@ -1956,52 +1956,52 @@
         <v>109253128.930002</v>
       </c>
       <c r="AF2" s="4" t="n">
-        <v>131674082.109994</v>
+        <v>131688828.609994</v>
       </c>
       <c r="AG2" s="4" t="n">
-        <v>118220412.020005</v>
+        <v>118467264.760005</v>
       </c>
       <c r="AH2" s="4" t="n">
-        <v>224058895.389808</v>
+        <v>224380337.439808</v>
       </c>
       <c r="AI2" s="4" t="n">
-        <v>146745288.997671</v>
+        <v>146671043.477671</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>259851380.5199911</v>
+        <v>260307157.6499911</v>
       </c>
       <c r="AK2" s="4" t="n">
-        <v>139600881.739279</v>
+        <v>139692913.109279</v>
       </c>
       <c r="AL2" s="4" t="n">
-        <v>237413824.909071</v>
+        <v>237474897.379071</v>
       </c>
       <c r="AM2" s="4" t="n">
-        <v>161124551.3899811</v>
+        <v>161156737.999981</v>
       </c>
       <c r="AN2" s="4" t="n">
-        <v>158991298.19001</v>
+        <v>159071928.55001</v>
       </c>
       <c r="AO2" s="4" t="n">
-        <v>176492615.569938</v>
+        <v>176545891.239938</v>
       </c>
       <c r="AP2" s="4" t="n">
-        <v>211502009.029984</v>
+        <v>211707164.399984</v>
       </c>
       <c r="AQ2" s="4" t="n">
-        <v>180782401.140012</v>
+        <v>180921554.040012</v>
       </c>
       <c r="AR2" s="4" t="n">
-        <v>152370609.009992</v>
+        <v>152449176.729992</v>
       </c>
       <c r="AS2" s="4" t="n">
-        <v>189067889.470009</v>
+        <v>189247757.610009</v>
       </c>
       <c r="AT2" s="4" t="n">
-        <v>165518516.18</v>
+        <v>165745823.46</v>
       </c>
       <c r="AU2" s="4" t="n">
-        <v>214932889.2099999</v>
+        <v>215039860.7399999</v>
       </c>
     </row>
     <row r="3">
@@ -2065,19 +2065,19 @@
         <v>84396209.80000001</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>77677370.84</v>
+        <v>80818642.39999999</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>77333450.97999999</v>
+        <v>81295834.81999999</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>127729395.89</v>
+        <v>136352759.13</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>157409014.59</v>
+        <v>166730799.29</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>115653351.38</v>
+        <v>120692187.6</v>
       </c>
       <c r="Y3" s="4" t="n">
         <v>186366659.95</v>
@@ -2101,52 +2101,52 @@
         <v>159763694.4</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>159227262.51</v>
+        <v>160301255.37</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>136119854.94</v>
+        <v>137069954.94</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>267629957.8</v>
+        <v>269818405.3000001</v>
       </c>
       <c r="AI3" s="4" t="n">
-        <v>205974435.75</v>
+        <v>206538287.21</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>307397794.89</v>
+        <v>308494543.02</v>
       </c>
       <c r="AK3" s="4" t="n">
-        <v>175008725.82</v>
+        <v>175429413.89</v>
       </c>
       <c r="AL3" s="4" t="n">
-        <v>306028126.6379</v>
+        <v>306720283.9279</v>
       </c>
       <c r="AM3" s="4" t="n">
-        <v>239729334.909375</v>
+        <v>238621838.409375</v>
       </c>
       <c r="AN3" s="4" t="n">
-        <v>154076904.2763</v>
+        <v>154309061.3663</v>
       </c>
       <c r="AO3" s="4" t="n">
-        <v>210184472.461525</v>
+        <v>210548151.211525</v>
       </c>
       <c r="AP3" s="4" t="n">
-        <v>263309306.762275</v>
+        <v>264640800.712275</v>
       </c>
       <c r="AQ3" s="4" t="n">
-        <v>213062881.0714</v>
+        <v>213730034.3214</v>
       </c>
       <c r="AR3" s="4" t="n">
-        <v>158759645.620525</v>
+        <v>159587902.090525</v>
       </c>
       <c r="AS3" s="4" t="n">
-        <v>183588122.124125</v>
+        <v>184438047.414125</v>
       </c>
       <c r="AT3" s="4" t="n">
-        <v>216342341.1</v>
+        <v>218094496.79</v>
       </c>
       <c r="AU3" s="4" t="n">
-        <v>222233601.61</v>
+        <v>224077610.83</v>
       </c>
     </row>
     <row r="4">
@@ -2192,106 +2192,106 @@
         <v>9447138.329999998</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>30728167.99</v>
+        <v>30669415.81</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>15807731.07</v>
+        <v>15836866.92</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>33448628.85</v>
+        <v>33583847.14</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>22191945.16</v>
+        <v>22223538.5</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>24497406.72</v>
+        <v>24474187.73</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>15786476.02</v>
+        <v>15815893.09</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>19390778.58</v>
+        <v>19431045.75</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>19730088.09</v>
+        <v>19761288.89</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>28857526.34</v>
+        <v>28948481.07</v>
       </c>
       <c r="W4" s="4" t="n">
-        <v>31871340.15999999</v>
+        <v>31901891.41999999</v>
       </c>
       <c r="X4" s="4" t="n">
-        <v>23237312.89000001</v>
+        <v>23269222.18000001</v>
       </c>
       <c r="Y4" s="4" t="n">
-        <v>26388198.18999999</v>
+        <v>26465754.93999999</v>
       </c>
       <c r="Z4" s="4" t="n">
-        <v>30723958.86000001</v>
+        <v>30877374.40000001</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>13839659.62000001</v>
+        <v>13762860.43000001</v>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>26510715.50857499</v>
+        <v>26513190.57857499</v>
       </c>
       <c r="AC4" s="4" t="n">
-        <v>27651203.2892</v>
+        <v>27735002.95919999</v>
       </c>
       <c r="AD4" s="4" t="n">
-        <v>25777893.302825</v>
+        <v>25808260.112825</v>
       </c>
       <c r="AE4" s="4" t="n">
-        <v>21471070.82215</v>
+        <v>21546022.84215</v>
       </c>
       <c r="AF4" s="4" t="n">
-        <v>25218038.272598</v>
+        <v>25282444.202598</v>
       </c>
       <c r="AG4" s="4" t="n">
-        <v>23076401.650775</v>
+        <v>23069008.30077501</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>41942043.20702499</v>
+        <v>41942587.84702499</v>
       </c>
       <c r="AI4" s="4" t="n">
-        <v>28168974.31117501</v>
+        <v>28213935.08117501</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>49349311.41459998</v>
+        <v>49376348.97459999</v>
       </c>
       <c r="AK4" s="4" t="n">
-        <v>24610663.58937501</v>
+        <v>24627521.51937501</v>
       </c>
       <c r="AL4" s="4" t="n">
-        <v>43707033.07519999</v>
+        <v>43695138.68519999</v>
       </c>
       <c r="AM4" s="4" t="n">
-        <v>30749965.66255001</v>
+        <v>30750620.28255001</v>
       </c>
       <c r="AN4" s="4" t="n">
-        <v>26973496.1157</v>
+        <v>27013954.2057</v>
       </c>
       <c r="AO4" s="4" t="n">
-        <v>30797595.83757502</v>
+        <v>30854963.39757502</v>
       </c>
       <c r="AP4" s="4" t="n">
-        <v>36909769.59110001</v>
+        <v>36958018.01110001</v>
       </c>
       <c r="AQ4" s="4" t="n">
-        <v>35793788.2699</v>
+        <v>35761872.9199</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>31353655.682575</v>
+        <v>31400468.422575</v>
       </c>
       <c r="AS4" s="4" t="n">
-        <v>39514732.761875</v>
+        <v>39591328.161875</v>
       </c>
       <c r="AT4" s="4" t="n">
-        <v>35734133.27892499</v>
+        <v>35804896.538925</v>
       </c>
       <c r="AU4" s="4" t="n">
-        <v>41978568.23534998</v>
+        <v>42171930.07534998</v>
       </c>
     </row>
     <row r="5">
@@ -2391,52 +2391,52 @@
         <v>11578398.15557499</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>19137183.05425</v>
+        <v>19571441.45425</v>
       </c>
       <c r="AG5" s="4" t="n">
-        <v>15340738.66835</v>
+        <v>15579009.38835</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>25217117.89282496</v>
+        <v>25574321.88282496</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>19525456.660475</v>
+        <v>19639473.520475</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>24753343.87617499</v>
+        <v>25035348.82617499</v>
       </c>
       <c r="AK5" s="4" t="n">
-        <v>14915495.28795</v>
+        <v>15004858.55795</v>
       </c>
       <c r="AL5" s="4" t="n">
-        <v>25094883.0311</v>
+        <v>25049015.0411</v>
       </c>
       <c r="AM5" s="4" t="n">
-        <v>15681125.679625</v>
+        <v>15439061.819625</v>
       </c>
       <c r="AN5" s="4" t="n">
-        <v>16339834.29305</v>
+        <v>16451810.89305</v>
       </c>
       <c r="AO5" s="4" t="n">
-        <v>17067459.3054</v>
+        <v>17202233.7854</v>
       </c>
       <c r="AP5" s="4" t="n">
-        <v>22728520.80794939</v>
+        <v>22837411.38794939</v>
       </c>
       <c r="AQ5" s="4" t="n">
-        <v>21102426.69577488</v>
+        <v>21333029.15577488</v>
       </c>
       <c r="AR5" s="4" t="n">
-        <v>19439194.42894998</v>
+        <v>19527599.40894998</v>
       </c>
       <c r="AS5" s="4" t="n">
-        <v>21004278.0010996</v>
+        <v>21188943.6710996</v>
       </c>
       <c r="AT5" s="4" t="n">
-        <v>21833926.48475001</v>
+        <v>22166785.91475001</v>
       </c>
       <c r="AU5" s="4" t="n">
-        <v>25173231.68885</v>
+        <v>25479432.11885</v>
       </c>
     </row>
     <row r="6">
@@ -2642,7 +2642,7 @@
         <v>3239296.030000001</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>3098640.189999999</v>
+        <v>3091012.149999999</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>3386822.119999999</v>
@@ -2654,76 +2654,76 @@
         <v>5169764.399999999</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>23526629.94</v>
+        <v>23503912.42</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>17706130.47000001</v>
+        <v>17720865.84</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>10275803.24</v>
+        <v>10260217.73</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>9280972.790000001</v>
+        <v>9294507.33</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>10547688.65095</v>
+        <v>10553476.01095</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>10309009.318075</v>
+        <v>10305529.188075</v>
       </c>
       <c r="AD7" s="4" t="n">
-        <v>11124056.49685</v>
+        <v>11138494.59685</v>
       </c>
       <c r="AE7" s="4" t="n">
-        <v>7598357.48255</v>
+        <v>7609642.70255</v>
       </c>
       <c r="AF7" s="4" t="n">
-        <v>9123369.6614</v>
+        <v>12998722.3814</v>
       </c>
       <c r="AG7" s="4" t="n">
-        <v>7835401.145749998</v>
+        <v>11245837.41575</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>12757698.161125</v>
+        <v>17951490.631125</v>
       </c>
       <c r="AI7" s="4" t="n">
-        <v>12629491.1487</v>
+        <v>14356490.3187</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>20192490.647275</v>
+        <v>27718259.357275</v>
       </c>
       <c r="AK7" s="4" t="n">
-        <v>6819684.550474998</v>
+        <v>6041430.490474997</v>
       </c>
       <c r="AL7" s="4" t="n">
-        <v>12454331.12605</v>
+        <v>16407849.67604999</v>
       </c>
       <c r="AM7" s="4" t="n">
-        <v>12451742.95925</v>
+        <v>8694580.43925</v>
       </c>
       <c r="AN7" s="4" t="n">
-        <v>12793666.681775</v>
+        <v>16209845.601775</v>
       </c>
       <c r="AO7" s="4" t="n">
-        <v>14242893.451175</v>
+        <v>17427037.151175</v>
       </c>
       <c r="AP7" s="4" t="n">
-        <v>20076850.588575</v>
+        <v>25209647.288575</v>
       </c>
       <c r="AQ7" s="4" t="n">
-        <v>17797333.33405</v>
+        <v>23128608.61405</v>
       </c>
       <c r="AR7" s="4" t="n">
-        <v>15331937.638775</v>
+        <v>19263435.298775</v>
       </c>
       <c r="AS7" s="4" t="n">
-        <v>19558367.33325</v>
+        <v>25647654.79325</v>
       </c>
       <c r="AT7" s="4" t="n">
-        <v>15149049.208825</v>
+        <v>18936582.678825</v>
       </c>
       <c r="AU7" s="4" t="n">
-        <v>19866224.8095</v>
+        <v>26822108.9395</v>
       </c>
     </row>
     <row r="8">
@@ -2805,70 +2805,70 @@
         <v>34935303.25000001</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>38989118.35000001</v>
+        <v>39524138.03000001</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>28317210.63999999</v>
+        <v>28486658.52</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>32429400.63050001</v>
+        <v>32519357.13050001</v>
       </c>
       <c r="AC8" s="4" t="n">
-        <v>31926657.62035001</v>
+        <v>32104894.85035001</v>
       </c>
       <c r="AD8" s="4" t="n">
-        <v>31392947.263275</v>
+        <v>31823562.753275</v>
       </c>
       <c r="AE8" s="4" t="n">
-        <v>25704386.61377496</v>
+        <v>25911677.28377496</v>
       </c>
       <c r="AF8" s="4" t="n">
-        <v>28892857.63384999</v>
+        <v>31519473.66384999</v>
       </c>
       <c r="AG8" s="4" t="n">
-        <v>29018006.98717501</v>
+        <v>32775958.14717501</v>
       </c>
       <c r="AH8" s="4" t="n">
-        <v>50578158.723275</v>
+        <v>56080177.763275</v>
       </c>
       <c r="AI8" s="4" t="n">
-        <v>35294992.15659999</v>
+        <v>37371030.00659999</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>58977889.79004999</v>
+        <v>64302229.64004999</v>
       </c>
       <c r="AK8" s="4" t="n">
-        <v>27901679.44225001</v>
+        <v>28463300.35225001</v>
       </c>
       <c r="AL8" s="4" t="n">
-        <v>49978324.61765</v>
+        <v>52378701.89765</v>
       </c>
       <c r="AM8" s="4" t="n">
-        <v>37607493.08107501</v>
+        <v>37012815.351075</v>
       </c>
       <c r="AN8" s="4" t="n">
-        <v>31536946.27272499</v>
+        <v>33783611.42272499</v>
       </c>
       <c r="AO8" s="4" t="n">
-        <v>40106902.975775</v>
+        <v>42218539.935775</v>
       </c>
       <c r="AP8" s="4" t="n">
-        <v>33241279.836675</v>
+        <v>43727306.556675</v>
       </c>
       <c r="AQ8" s="4" t="n">
-        <v>32327155.23485</v>
+        <v>42177021.58485</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>22989262.893575</v>
+        <v>25686640.963575</v>
       </c>
       <c r="AS8" s="4" t="n">
-        <v>29430899.208075</v>
+        <v>33095326.338075</v>
       </c>
       <c r="AT8" s="4" t="n">
-        <v>40467572.591975</v>
+        <v>43751696.421975</v>
       </c>
       <c r="AU8" s="4" t="n">
-        <v>27217019.434475</v>
+        <v>31417286.124475</v>
       </c>
     </row>
   </sheetData>
@@ -3176,52 +3176,52 @@
         <v>0.08023963805602773</v>
       </c>
       <c r="AF2" s="5" t="n">
-        <v>0.1045822633614391</v>
+        <v>0.104523112813842</v>
       </c>
       <c r="AG2" s="5" t="n">
-        <v>0.08223878349731131</v>
+        <v>0.08233131146971379</v>
       </c>
       <c r="AH2" s="5" t="n">
-        <v>0.09609357303884287</v>
+        <v>0.09610054174465864</v>
       </c>
       <c r="AI2" s="5" t="n">
-        <v>0.06171241529173074</v>
+        <v>0.06161630980269218</v>
       </c>
       <c r="AJ2" s="5" t="n">
-        <v>0.1072580559519872</v>
+        <v>0.1072756888868364</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>0.06103551310612697</v>
+        <v>0.06093940045882699</v>
       </c>
       <c r="AL2" s="5" t="n">
-        <v>0.09899261881443813</v>
+        <v>0.09892587967425039</v>
       </c>
       <c r="AM2" s="5" t="n">
-        <v>0.08247881902196726</v>
+        <v>0.08242024688525044</v>
       </c>
       <c r="AN2" s="5" t="n">
-        <v>0.06572900798343892</v>
+        <v>0.06570283919635327</v>
       </c>
       <c r="AO2" s="5" t="n">
-        <v>0.09123159530492243</v>
+        <v>0.0911853336533613</v>
       </c>
       <c r="AP2" s="5" t="n">
-        <v>0.1085843726413652</v>
+        <v>0.1086002675966543</v>
       </c>
       <c r="AQ2" s="5" t="n">
-        <v>0.1161267839611031</v>
+        <v>0.1161082916692503</v>
       </c>
       <c r="AR2" s="5" t="n">
-        <v>0.1056276269317268</v>
+        <v>0.1055992582198185</v>
       </c>
       <c r="AS2" s="5" t="n">
-        <v>0.1087476175528774</v>
+        <v>0.108759000476182</v>
       </c>
       <c r="AT2" s="5" t="n">
-        <v>0.06212119116953187</v>
+        <v>0.06215166385864119</v>
       </c>
       <c r="AU2" s="5" t="n">
-        <v>0.08429755018316638</v>
+        <v>0.0842598256616261</v>
       </c>
     </row>
     <row r="3">
@@ -3285,19 +3285,19 @@
         <v>0.1148353091700614</v>
       </c>
       <c r="T3" s="5" t="n">
-        <v>0.1127303995057735</v>
+        <v>0.1112483325141863</v>
       </c>
       <c r="U3" s="5" t="n">
-        <v>0.1063510430931255</v>
+        <v>0.1043043465508367</v>
       </c>
       <c r="V3" s="5" t="n">
-        <v>0.1138366871889274</v>
+        <v>0.1122408636295253</v>
       </c>
       <c r="W3" s="5" t="n">
-        <v>0.09978972785376292</v>
+        <v>0.09975603246230484</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>0.06693887340937078</v>
+        <v>0.06602890036898285</v>
       </c>
       <c r="Y3" s="5" t="n">
         <v>0.1132457331009819</v>
@@ -3321,52 +3321,52 @@
         <v>0.1257375549574911</v>
       </c>
       <c r="AF3" s="5" t="n">
-        <v>0.1246889908721435</v>
+        <v>0.1248361698429396</v>
       </c>
       <c r="AG3" s="5" t="n">
-        <v>0.09819127101833662</v>
+        <v>0.0984723292389119</v>
       </c>
       <c r="AH3" s="5" t="n">
-        <v>0.1207781953932788</v>
+        <v>0.1210839153474212</v>
       </c>
       <c r="AI3" s="5" t="n">
-        <v>0.0808278233148176</v>
+        <v>0.08066641988873471</v>
       </c>
       <c r="AJ3" s="5" t="n">
-        <v>0.1126179452681737</v>
+        <v>0.1125349413341032</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>0.06525931481610683</v>
+        <v>0.06515602430422282</v>
       </c>
       <c r="AL3" s="5" t="n">
-        <v>0.1140519031238825</v>
+        <v>0.1138525234190431</v>
       </c>
       <c r="AM3" s="5" t="n">
-        <v>0.119703936651648</v>
+        <v>0.1186678168131747</v>
       </c>
       <c r="AN3" s="5" t="n">
-        <v>0.06331196531391313</v>
+        <v>0.06314207807325049</v>
       </c>
       <c r="AO3" s="5" t="n">
-        <v>0.1010926461378692</v>
+        <v>0.1008512323155822</v>
       </c>
       <c r="AP3" s="5" t="n">
-        <v>0.1329822144597282</v>
+        <v>0.133068185203923</v>
       </c>
       <c r="AQ3" s="5" t="n">
-        <v>0.1476370061856506</v>
+        <v>0.1473974940463366</v>
       </c>
       <c r="AR3" s="5" t="n">
-        <v>0.1216433456673416</v>
+        <v>0.1216308212745299</v>
       </c>
       <c r="AS3" s="5" t="n">
-        <v>0.1180775041710639</v>
+        <v>0.1180152609108509</v>
       </c>
       <c r="AT3" s="5" t="n">
-        <v>0.0923608206654183</v>
+        <v>0.09260460176898894</v>
       </c>
       <c r="AU3" s="5" t="n">
-        <v>0.08764102145194559</v>
+        <v>0.08798277382905301</v>
       </c>
     </row>
     <row r="4">
@@ -3412,106 +3412,106 @@
         <v>0.06677652114618168</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0.09011855584300205</v>
+        <v>0.08933940214275587</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>0.06707488571689614</v>
+        <v>0.06682152158621732</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.1041869605955468</v>
+        <v>0.1041723614001354</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>0.08016041637559229</v>
+        <v>0.07996237154016758</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>0.1124064112763967</v>
+        <v>0.1118318501183127</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>0.08807886735021359</v>
+        <v>0.08796901734071662</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>0.1101384396122375</v>
+        <v>0.1101087552892006</v>
       </c>
       <c r="U4" s="5" t="n">
-        <v>0.1041240645547944</v>
+        <v>0.1039767205742088</v>
       </c>
       <c r="V4" s="5" t="n">
-        <v>0.09688904092059383</v>
+        <v>0.09678139349449659</v>
       </c>
       <c r="W4" s="5" t="n">
-        <v>0.09105264103733007</v>
+        <v>0.09078591460042634</v>
       </c>
       <c r="X4" s="5" t="n">
-        <v>0.06065354199014373</v>
+        <v>0.06042057982643384</v>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>0.08469236513514861</v>
+        <v>0.08443620084701435</v>
       </c>
       <c r="Z4" s="5" t="n">
-        <v>0.09128301747443576</v>
+        <v>0.09127031827280552</v>
       </c>
       <c r="AA4" s="5" t="n">
-        <v>0.04359441388356023</v>
+        <v>0.04314973285816799</v>
       </c>
       <c r="AB4" s="5" t="n">
-        <v>0.06171602077021029</v>
+        <v>0.06148343283820458</v>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>0.07811166564015416</v>
+        <v>0.07803997492304258</v>
       </c>
       <c r="AD4" s="5" t="n">
-        <v>0.08023703713669871</v>
+        <v>0.08004389444336914</v>
       </c>
       <c r="AE4" s="5" t="n">
-        <v>0.07713949246796831</v>
+        <v>0.07720712549175776</v>
       </c>
       <c r="AF4" s="5" t="n">
-        <v>0.105272625091332</v>
+        <v>0.1052735682822191</v>
       </c>
       <c r="AG4" s="5" t="n">
-        <v>0.07389529118240473</v>
+        <v>0.07366429514954072</v>
       </c>
       <c r="AH4" s="5" t="n">
-        <v>0.1015378653695578</v>
+        <v>0.1011286371112304</v>
       </c>
       <c r="AI4" s="5" t="n">
-        <v>0.06065000893018747</v>
+        <v>0.06053048318334737</v>
       </c>
       <c r="AJ4" s="5" t="n">
-        <v>0.09497872840604099</v>
+        <v>0.09458845318920554</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>0.04736850463641674</v>
+        <v>0.04723614147024539</v>
       </c>
       <c r="AL4" s="5" t="n">
-        <v>0.08403965723304499</v>
+        <v>0.08372112528155469</v>
       </c>
       <c r="AM4" s="5" t="n">
-        <v>0.07919196002815583</v>
+        <v>0.07883249199166542</v>
       </c>
       <c r="AN4" s="5" t="n">
-        <v>0.05470870693371566</v>
+        <v>0.05460058910576588</v>
       </c>
       <c r="AO4" s="5" t="n">
-        <v>0.07930522957374392</v>
+        <v>0.07915444945148352</v>
       </c>
       <c r="AP4" s="5" t="n">
-        <v>0.09457734403183861</v>
+        <v>0.09443906830925246</v>
       </c>
       <c r="AQ4" s="5" t="n">
-        <v>0.1154937110947032</v>
+        <v>0.1151568710854199</v>
       </c>
       <c r="AR4" s="5" t="n">
-        <v>0.0956425901605318</v>
+        <v>0.09562853882815639</v>
       </c>
       <c r="AS4" s="5" t="n">
-        <v>0.1095774798759749</v>
+        <v>0.1094250079901788</v>
       </c>
       <c r="AT4" s="5" t="n">
-        <v>0.07918670195337527</v>
+        <v>0.07875439706386798</v>
       </c>
       <c r="AU4" s="5" t="n">
-        <v>0.09534616967942637</v>
+        <v>0.09508152713328677</v>
       </c>
     </row>
     <row r="5">
@@ -3611,52 +3611,52 @@
         <v>0.04924760769540809</v>
       </c>
       <c r="AF5" s="5" t="n">
-        <v>0.08822325581139394</v>
+        <v>0.08951044708116858</v>
       </c>
       <c r="AG5" s="5" t="n">
-        <v>0.06472187275938412</v>
+        <v>0.06529457748421899</v>
       </c>
       <c r="AH5" s="5" t="n">
-        <v>0.08321503415369309</v>
+        <v>0.08391261196743025</v>
       </c>
       <c r="AI5" s="5" t="n">
-        <v>0.06070838617080095</v>
+        <v>0.06071394256977217</v>
       </c>
       <c r="AJ5" s="5" t="n">
-        <v>0.06924386807424526</v>
+        <v>0.06968929332548454</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>0.04360250206016076</v>
+        <v>0.04361872842254786</v>
       </c>
       <c r="AL5" s="5" t="n">
-        <v>0.07148799903340412</v>
+        <v>0.0709343844798523</v>
       </c>
       <c r="AM5" s="5" t="n">
-        <v>0.05586376886786126</v>
+        <v>0.05471250053525075</v>
       </c>
       <c r="AN5" s="5" t="n">
-        <v>0.04707304671521379</v>
+        <v>0.04716694058597888</v>
       </c>
       <c r="AO5" s="5" t="n">
-        <v>0.05630864332374759</v>
+        <v>0.05649182312874251</v>
       </c>
       <c r="AP5" s="5" t="n">
-        <v>0.07930089483625891</v>
+        <v>0.07925410228824659</v>
       </c>
       <c r="AQ5" s="5" t="n">
-        <v>0.1007442236371696</v>
+        <v>0.1013911806427037</v>
       </c>
       <c r="AR5" s="5" t="n">
-        <v>0.08970005867065924</v>
+        <v>0.08977172884381385</v>
       </c>
       <c r="AS5" s="5" t="n">
-        <v>0.08083852363424211</v>
+        <v>0.08125166386183696</v>
       </c>
       <c r="AT5" s="5" t="n">
-        <v>0.06222116686931414</v>
+        <v>0.06281713256953658</v>
       </c>
       <c r="AU5" s="5" t="n">
-        <v>0.07163226054676371</v>
+        <v>0.07209004754628903</v>
       </c>
     </row>
     <row r="6">
@@ -3862,7 +3862,7 @@
         <v>0.06097878084823251</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>0.07671956441403846</v>
+        <v>0.07643000187770788</v>
       </c>
       <c r="U7" s="5" t="n">
         <v>0.06295288932039939</v>
@@ -3874,76 +3874,76 @@
         <v>0.06797748989012485</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>0.1218988317740848</v>
+        <v>0.1217811251941</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>0.08429483741476367</v>
+        <v>0.08425829087891586</v>
       </c>
       <c r="Z7" s="5" t="n">
-        <v>0.04536763402339741</v>
+        <v>0.04525279775341109</v>
       </c>
       <c r="AA7" s="5" t="n">
-        <v>0.06070322926729252</v>
+        <v>0.06077275917112652</v>
       </c>
       <c r="AB7" s="5" t="n">
-        <v>0.05321703038708214</v>
+        <v>0.05322085252515482</v>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>0.06219205197625542</v>
+        <v>0.06214221710759328</v>
       </c>
       <c r="AD7" s="5" t="n">
-        <v>0.08675284464603276</v>
+        <v>0.08681112956299057</v>
       </c>
       <c r="AE7" s="5" t="n">
-        <v>0.07675728413539434</v>
+        <v>0.0768134708438455</v>
       </c>
       <c r="AF7" s="5" t="n">
-        <v>0.08948374619171583</v>
+        <v>0.08602509817384077</v>
       </c>
       <c r="AG7" s="5" t="n">
-        <v>0.06899772132526946</v>
+        <v>0.06575538701079545</v>
       </c>
       <c r="AH7" s="5" t="n">
-        <v>0.07364068332410174</v>
+        <v>0.06873579644923303</v>
       </c>
       <c r="AI7" s="5" t="n">
-        <v>0.05363264557834609</v>
+        <v>0.04223047244581379</v>
       </c>
       <c r="AJ7" s="5" t="n">
-        <v>0.079729330119808</v>
+        <v>0.07609963795315254</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>0.02588789672839217</v>
+        <v>0.01614275360520561</v>
       </c>
       <c r="AL7" s="5" t="n">
-        <v>0.04459646423952119</v>
+        <v>0.04199037677028461</v>
       </c>
       <c r="AM7" s="5" t="n">
-        <v>0.04611520111165042</v>
+        <v>0.02429391780877503</v>
       </c>
       <c r="AN7" s="5" t="n">
-        <v>0.04514287740485656</v>
+        <v>0.04070021191754183</v>
       </c>
       <c r="AO7" s="5" t="n">
-        <v>0.06530546399973894</v>
+        <v>0.05596483838871727</v>
       </c>
       <c r="AP7" s="5" t="n">
-        <v>0.09491480064448742</v>
+        <v>0.08621905740091315</v>
       </c>
       <c r="AQ7" s="5" t="n">
-        <v>0.1018201570154388</v>
+        <v>0.09389257316890445</v>
       </c>
       <c r="AR7" s="5" t="n">
-        <v>0.1010994669232503</v>
+        <v>0.09427043756266028</v>
       </c>
       <c r="AS7" s="5" t="n">
-        <v>0.1013555928940227</v>
+        <v>0.101259883542212</v>
       </c>
       <c r="AT7" s="5" t="n">
-        <v>0.05735717629802643</v>
+        <v>0.05287261702159167</v>
       </c>
       <c r="AU7" s="5" t="n">
-        <v>0.07207956562196247</v>
+        <v>0.07156633180829659</v>
       </c>
     </row>
     <row r="8">
@@ -4025,70 +4025,70 @@
         <v>0.08080059266557206</v>
       </c>
       <c r="Z8" s="5" t="n">
-        <v>0.08694683238403508</v>
+        <v>0.08710082999726887</v>
       </c>
       <c r="AA8" s="5" t="n">
-        <v>0.06911149282834277</v>
+        <v>0.06907778595388753</v>
       </c>
       <c r="AB8" s="5" t="n">
-        <v>0.06335844387745047</v>
+        <v>0.06308255905374281</v>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>0.07546663349802553</v>
+        <v>0.07535300073958827</v>
       </c>
       <c r="AD8" s="5" t="n">
-        <v>0.08611794715607018</v>
+        <v>0.0866024968761536</v>
       </c>
       <c r="AE8" s="5" t="n">
-        <v>0.0735544067008406</v>
+        <v>0.07369408905628411</v>
       </c>
       <c r="AF8" s="5" t="n">
-        <v>0.09128700139468311</v>
+        <v>0.09160990483775704</v>
       </c>
       <c r="AG8" s="5" t="n">
-        <v>0.07753389379630855</v>
+        <v>0.08015944300964939</v>
       </c>
       <c r="AH8" s="5" t="n">
-        <v>0.09601885644148894</v>
+        <v>0.09800963144686428</v>
       </c>
       <c r="AI8" s="5" t="n">
-        <v>0.06101624712544645</v>
+        <v>0.05987018887631315</v>
       </c>
       <c r="AJ8" s="5" t="n">
-        <v>0.09374421415344827</v>
+        <v>0.09449648600164354</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>0.04696083304654258</v>
+        <v>0.04454104442417497</v>
       </c>
       <c r="AL8" s="5" t="n">
-        <v>0.08244654135295988</v>
+        <v>0.08021767118932323</v>
       </c>
       <c r="AM8" s="5" t="n">
-        <v>0.08086974097316414</v>
+        <v>0.07428229781770861</v>
       </c>
       <c r="AN8" s="5" t="n">
-        <v>0.05278635336113133</v>
+        <v>0.05299075453111409</v>
       </c>
       <c r="AO8" s="5" t="n">
-        <v>0.07931986714156788</v>
+        <v>0.07819602313841453</v>
       </c>
       <c r="AP8" s="5" t="n">
-        <v>0.08330865667331497</v>
+        <v>0.0870358205353053</v>
       </c>
       <c r="AQ8" s="5" t="n">
-        <v>0.10291433328192</v>
+        <v>0.1056204195169801</v>
       </c>
       <c r="AR8" s="5" t="n">
-        <v>0.09052022428237681</v>
+        <v>0.09292831257908445</v>
       </c>
       <c r="AS8" s="5" t="n">
-        <v>0.09727912570042034</v>
+        <v>0.100138057597633</v>
       </c>
       <c r="AT8" s="5" t="n">
-        <v>0.09009331565681629</v>
+        <v>0.08938553542332603</v>
       </c>
       <c r="AU8" s="5" t="n">
-        <v>0.08064610812884046</v>
+        <v>0.08240710655682863</v>
       </c>
     </row>
   </sheetData>
